--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1327">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:40:58+00:00</t>
+    <t>2026-07-29T17:09:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3858,6 +3858,10 @@
     <t>Kind of document (LOINC if possible)</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+</t>
+  </si>
+  <si>
     <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
   </si>
   <si>
@@ -3909,6 +3913,13 @@
 -	TRE_R02-SecteurActivite, OID : 1.2.250.1.71.4.2.4 (lorsque l’auteur du document est un professionnel ou un équipement sous sa responsabilité)
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J61-HealthcareFacilityTypeCode-DMP).
 En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J02-XdsHealthcareFacilityTypeCode-CISIS peut être utilisé. {null}</t>
+  </si>
+  <si>
+    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {context.sourcePatientInfo.reference.exists() implies context.sourcePatientInfo.reference.startsWith('#')}</t>
   </si>
   <si>
     <t>pdsm-submissionset-comprehensive</t>
@@ -5626,7 +5637,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="174">
@@ -5634,7 +5645,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="175">
@@ -5650,7 +5661,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="177">
@@ -5658,7 +5669,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="178">
@@ -5712,7 +5723,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="185">
@@ -5756,7 +5767,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="191">
@@ -73402,10 +73413,10 @@
         <v>85</v>
       </c>
       <c r="L648" t="s" s="2">
-        <v>234</v>
+        <v>1233</v>
       </c>
       <c r="M648" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N648" t="s" s="2">
         <v>236</v>
@@ -73610,7 +73621,7 @@
         <v>85</v>
       </c>
       <c r="L650" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="M650" t="s" s="2">
         <v>244</v>
@@ -73928,10 +73939,10 @@
         <v>258</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>261</v>
@@ -73996,7 +74007,7 @@
         <v>75</v>
       </c>
       <c r="AK653" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="654">
@@ -74348,7 +74359,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>273</v>
@@ -74416,7 +74427,7 @@
         <v>75</v>
       </c>
       <c r="AK657" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="658">
@@ -74453,7 +74464,7 @@
         <v>278</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>280</v>
@@ -74519,7 +74530,7 @@
         <v>75</v>
       </c>
       <c r="AK658" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="659">
@@ -74556,7 +74567,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74768,7 +74779,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75707,7 +75718,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75814,7 +75825,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76240,7 +76251,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77243,7 +77254,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="685">
@@ -77348,7 +77359,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="686">
@@ -77382,10 +77393,10 @@
         <v>75</v>
       </c>
       <c r="L686" t="s" s="2">
-        <v>234</v>
+        <v>1233</v>
       </c>
       <c r="M686" t="s" s="2">
-        <v>415</v>
+        <v>1249</v>
       </c>
       <c r="N686" t="s" s="2">
         <v>416</v>
@@ -77451,7 +77462,7 @@
         <v>75</v>
       </c>
       <c r="AK686" t="s" s="2">
-        <v>96</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="687">
@@ -77561,7 +77572,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77664,7 +77675,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77769,7 +77780,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77872,7 +77883,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77975,7 +77986,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78080,7 +78091,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78185,7 +78196,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78290,7 +78301,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78395,7 +78406,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78500,7 +78511,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78605,7 +78616,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78710,7 +78721,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78815,7 +78826,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78920,7 +78931,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79025,7 +79036,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79057,7 +79068,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79130,7 +79141,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79144,7 +79155,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79231,7 +79242,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79265,7 +79276,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79331,18 +79342,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1257</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79439,13 +79450,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79542,13 +79553,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79588,7 +79599,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79647,13 +79658,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79713,7 +79724,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79748,16 +79759,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79779,13 +79790,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="M709" t="s" s="2">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="N709" t="s" s="2">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79853,16 +79864,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79884,13 +79895,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79958,10 +79969,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -79992,7 +80003,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80063,16 +80074,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80094,10 +80105,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80168,13 +80179,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80271,13 +80282,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80374,13 +80385,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80479,13 +80490,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80582,7 +80593,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80685,7 +80696,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80786,7 +80797,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80817,10 +80828,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80891,7 +80902,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80925,7 +80936,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -80996,7 +81007,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81028,7 +81039,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81101,7 +81112,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81133,7 +81144,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81208,7 +81219,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81240,7 +81251,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81313,7 +81324,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81345,7 +81356,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81364,7 +81375,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81418,7 +81429,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81525,7 +81536,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81628,7 +81639,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81660,7 +81671,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81735,7 +81746,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81764,10 +81775,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81842,13 +81853,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81945,13 +81956,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82050,16 +82061,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="D731" t="s" s="2">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82081,13 +82092,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82155,13 +82166,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82258,13 +82269,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82361,13 +82372,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82407,7 +82418,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82466,13 +82477,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82495,7 +82506,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82569,13 +82580,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82674,13 +82685,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82779,13 +82790,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82884,13 +82895,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82989,7 +83000,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83096,7 +83107,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83128,7 +83139,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83199,7 +83210,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83231,7 +83242,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83304,7 +83315,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83407,7 +83418,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83512,7 +83523,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83619,7 +83630,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83726,7 +83737,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83835,7 +83846,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83940,7 +83951,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83969,10 +83980,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84043,7 +84054,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24929" uniqueCount="1326">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:09:31+00:00</t>
+    <t>2026-07-30T07:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3858,10 +3858,6 @@
     <t>Kind of document (LOINC if possible)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
-</t>
-  </si>
-  <si>
     <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
   </si>
   <si>
@@ -3915,7 +3911,7 @@
 En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J02-XdsHealthcareFacilityTypeCode-CISIS peut être utilisé. {null}</t>
   </si>
   <si>
-    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi).</t>
+    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi) qui hérite de profil FR Core Patient.</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -5637,7 +5633,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="174">
@@ -5645,7 +5641,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="175">
@@ -5661,7 +5657,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="177">
@@ -5669,7 +5665,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="178">
@@ -5723,7 +5719,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="185">
@@ -5767,7 +5763,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="191">
@@ -73413,10 +73409,10 @@
         <v>85</v>
       </c>
       <c r="L648" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M648" t="s" s="2">
         <v>1233</v>
-      </c>
-      <c r="M648" t="s" s="2">
-        <v>1234</v>
       </c>
       <c r="N648" t="s" s="2">
         <v>236</v>
@@ -73621,7 +73617,7 @@
         <v>85</v>
       </c>
       <c r="L650" t="s" s="2">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="M650" t="s" s="2">
         <v>244</v>
@@ -73939,10 +73935,10 @@
         <v>258</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1235</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1236</v>
-      </c>
-      <c r="N653" t="s" s="2">
-        <v>1237</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>261</v>
@@ -74007,7 +74003,7 @@
         <v>75</v>
       </c>
       <c r="AK653" t="s" s="2">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="654">
@@ -74359,7 +74355,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>273</v>
@@ -74427,7 +74423,7 @@
         <v>75</v>
       </c>
       <c r="AK657" t="s" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="658">
@@ -74464,7 +74460,7 @@
         <v>278</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>280</v>
@@ -74530,7 +74526,7 @@
         <v>75</v>
       </c>
       <c r="AK658" t="s" s="2">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="659">
@@ -74567,7 +74563,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74779,7 +74775,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75718,7 +75714,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75825,7 +75821,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76251,7 +76247,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77254,7 +77250,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="685">
@@ -77359,7 +77355,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="686">
@@ -77393,10 +77389,10 @@
         <v>75</v>
       </c>
       <c r="L686" t="s" s="2">
-        <v>1233</v>
+        <v>234</v>
       </c>
       <c r="M686" t="s" s="2">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N686" t="s" s="2">
         <v>416</v>
@@ -77462,7 +77458,7 @@
         <v>75</v>
       </c>
       <c r="AK686" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="687">
@@ -77572,7 +77568,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77675,7 +77671,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77780,7 +77776,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77883,7 +77879,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77986,7 +77982,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78091,7 +78087,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78196,7 +78192,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78301,7 +78297,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78406,7 +78402,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78511,7 +78507,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78616,7 +78612,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78721,7 +78717,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78826,7 +78822,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78931,7 +78927,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79036,7 +79032,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79068,7 +79064,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79141,7 +79137,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79155,7 +79151,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79242,7 +79238,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79276,7 +79272,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79342,18 +79338,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1260</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1261</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1262</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79450,13 +79446,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1262</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1263</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1264</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79553,13 +79549,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1264</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1265</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79599,7 +79595,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79658,13 +79654,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1269</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79724,7 +79720,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79759,16 +79755,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79790,13 +79786,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="M709" t="s" s="2">
         <v>1273</v>
       </c>
-      <c r="M709" t="s" s="2">
+      <c r="N709" t="s" s="2">
         <v>1274</v>
-      </c>
-      <c r="N709" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79864,16 +79860,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79895,13 +79891,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1277</v>
+      </c>
+      <c r="M710" t="s" s="2">
         <v>1278</v>
       </c>
-      <c r="M710" t="s" s="2">
+      <c r="N710" t="s" s="2">
         <v>1279</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1280</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79969,10 +79965,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -80003,7 +79999,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80074,16 +80070,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80105,10 +80101,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="M712" t="s" s="2">
         <v>1285</v>
-      </c>
-      <c r="M712" t="s" s="2">
-        <v>1286</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80179,13 +80175,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80282,13 +80278,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80385,13 +80381,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80490,13 +80486,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80593,7 +80589,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80696,7 +80692,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80797,7 +80793,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80828,10 +80824,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
+        <v>1290</v>
+      </c>
+      <c r="M719" t="s" s="2">
         <v>1291</v>
-      </c>
-      <c r="M719" t="s" s="2">
-        <v>1292</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80902,7 +80898,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80936,7 +80932,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -81007,7 +81003,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81039,7 +81035,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81112,7 +81108,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81144,7 +81140,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81219,7 +81215,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81251,7 +81247,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81324,7 +81320,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81356,7 +81352,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81375,7 +81371,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81429,7 +81425,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81536,7 +81532,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81639,7 +81635,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81671,7 +81667,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81746,7 +81742,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81775,10 +81771,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
+        <v>1299</v>
+      </c>
+      <c r="M728" t="s" s="2">
         <v>1300</v>
-      </c>
-      <c r="M728" t="s" s="2">
-        <v>1301</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81853,13 +81849,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81956,13 +81952,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82061,16 +82057,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1303</v>
+      </c>
+      <c r="C731" t="s" s="2">
+        <v>1302</v>
+      </c>
+      <c r="D731" t="s" s="2">
         <v>1304</v>
-      </c>
-      <c r="C731" t="s" s="2">
-        <v>1303</v>
-      </c>
-      <c r="D731" t="s" s="2">
-        <v>1305</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82092,13 +82088,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
+        <v>1305</v>
+      </c>
+      <c r="M731" t="s" s="2">
         <v>1306</v>
       </c>
-      <c r="M731" t="s" s="2">
+      <c r="N731" t="s" s="2">
         <v>1307</v>
-      </c>
-      <c r="N731" t="s" s="2">
-        <v>1308</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82166,13 +82162,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1308</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1309</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1310</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82269,13 +82265,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1311</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1312</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82372,13 +82368,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1313</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1314</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82418,7 +82414,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82477,13 +82473,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82506,7 +82502,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82580,13 +82576,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82685,13 +82681,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82790,13 +82786,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82895,13 +82891,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83000,7 +82996,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83107,7 +83103,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83139,7 +83135,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83210,7 +83206,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83242,7 +83238,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83315,7 +83311,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83418,7 +83414,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83523,7 +83519,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83630,7 +83626,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83737,7 +83733,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83846,7 +83842,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83951,7 +83947,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83980,10 +83976,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
+        <v>1324</v>
+      </c>
+      <c r="M749" t="s" s="2">
         <v>1325</v>
-      </c>
-      <c r="M749" t="s" s="2">
-        <v>1326</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84054,7 +84050,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:55:20+00:00</t>
+    <t>2026-07-30T08:19:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3915,7 +3915,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {context.sourcePatientInfo.reference.exists() implies context.sourcePatientInfo.reference.startsWith('#')}</t>
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>pdsm-submissionset-comprehensive</t>

--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:19:35+00:00</t>
+    <t>2026-07-30T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:31:43+00:00</t>
+    <t>2026-07-30T10:07:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -77389,7 +77389,7 @@
         <v>75</v>
       </c>
       <c r="L686" t="s" s="2">
-        <v>234</v>
+        <v>414</v>
       </c>
       <c r="M686" t="s" s="2">
         <v>1248</v>

--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:07:17+00:00</t>
+    <t>2026-07-30T12:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3915,7 +3915,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {reference.exists() implies reference.startsWith('#')}</t>
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), cf spécifications IHE MHD ITI-105 §2:3.105.4.1.2.2. {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>pdsm-submissionset-comprehensive</t>
